--- a/Result/checksun_type/製管.xlsx
+++ b/Result/checksun_type/製管.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>57.27999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>59.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>56.01</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>56.01</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>59609.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>67935.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>67935</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>220934.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>164785.88</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>164785.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-46963.84747535645</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>59609</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>59609.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>57.44</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>55.94</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>54744.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>75071.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>75071.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>299075.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>165050.56</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>165050.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-43834.07601280449</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>54744</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>54744.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>59.82</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>55.9</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>55.9</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>61706.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>99783.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>99783</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>350760.4</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>165553.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>165553.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-37276.22120870152</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>61706</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>61706.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>58.42</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>59.87</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>55.83</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>55.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>90753.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>120848.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>120848</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>368661.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>165247.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>165247</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-27322.49215967229</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>90753</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>90753.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>58.86</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>59.88</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>55.76</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>55.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>72863.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>167434.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>167434.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>396389.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>164882.96</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>164882.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-15239.25451249938</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>72863</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>72863.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>59.62</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>59.72</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>55.67</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>59.72</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>55.67</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>95290.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>373933.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>373933.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>426980.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>164363.16</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>164363.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>4483.55835890834</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>95290</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>95290.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>61.96</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>59.66</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>55.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>178303.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>523079.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>523079.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>446366.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>163174.9</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>163174.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>30095.98537667264</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>178303</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>178303.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>62.82000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>59.54</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>55.49</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>59.54</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>55.49</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>167031.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>601737.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>601737.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>440987.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>160892.24</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>160892.24</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>56716.06021002628</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>167031</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>167031.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>63.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>59.35</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>55.4</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>59.35</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>55.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>323685.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>616475.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>616475.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>436133.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>158893.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>158893.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>93926.87925017328</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>323685</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>323685.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>63.64</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>59.14</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>55.32</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>55.32</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1105359.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>625344.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>625344</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>412792.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>153852.84</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>153852.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>126946.30362002</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1105359</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1105359.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>63.56</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>58.79</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>55.18</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>55.18</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>841018.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>480026.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>480026.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>313194.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>133772.3</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>133772.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>85832.32759051461</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>841018</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>841018.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>19.75</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>19.32</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>132621113.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>46668688.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>46668688.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>37930663.3</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>24467742.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>24467742.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>9216793.900870845</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>132621113</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>132621113.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>19.41</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>26830670.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>25226666.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>25226666</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>26250725.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>22382197.58</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>22382197.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>1377500.007797588</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>26830670</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>26830670.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>19.28</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>43465545.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>24261943.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>24261943.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>24604465.6</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>22403454.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>22403454.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>1464002.624557309</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>43465545</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>43465545.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>19.29</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>14439758.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>23879779.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>23879779.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>21672869.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>21839201.36</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>21839201.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-247016.0523772761</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>14439758</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>14439758.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>19.43</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>15986358.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>26971384.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>26971384.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>21268337.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>21836585.24</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>21836585.24</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>427399.3038724996</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>15986358</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>15986358.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>19.49</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>19.61</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>25410999.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>29192637.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>29192637.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>20825724.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>21906077.96</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>21906077.96</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>1209878.409091018</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>25410999</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>25410999.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>19.56</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>22007057.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>27274784.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>27274784</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>19852251.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>21873902.02</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>21873902.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>1274712.794792797</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>22007057</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>22007057.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>19.46</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>41554725.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24946987.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24946987.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>20320292.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>22642043.72</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>22642043.72</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1686515.96026703</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>41554725</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>41554725.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>19.44</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>19.64</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>29897782.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>19465959.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>19465959.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>19736315.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>22577403.58</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>22577403.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>120180.4837921113</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>29897782</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>29897782.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>19.45</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>27092626.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>15565290.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>15565290.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>18973182.0</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>22772553.22</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>22772553.22</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-872775.6070217751</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>27092626</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>27092626.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>18.98</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>15821730.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>12458810.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>12458810.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>18276539.7</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>22770756.54</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>22770756.54</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1959561.322219411</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>15821730</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>15821730.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>13.81</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13.95</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>7179558.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>2762810.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>2762810</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>3505525.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>3069694.86</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>3069694.86</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>93265.28022598708</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>7179558</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>7179558.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>13.81</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>13.95</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>707416.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>2040895.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>2040895.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3340599.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>3018115.32</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>3018115.32</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-293131.475576262</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>707416</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>707416.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>13.82</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>13.91</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13.95</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1135863.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3208393.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3208393.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3464739.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>3078372.74</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>3078372.74</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-141214.0740231802</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1135863</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1135863.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>13.86</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>13.96</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>13.96</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>2882804.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>3470879.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>3470879.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3567721.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>3115920.62</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>3115920.62</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>34949.10941062123</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>2882804</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>2882804.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>13.91</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>13.93</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13.97</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1908409.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>4299654.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>4299654.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3478735.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>3104062.26</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>3104062.26</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>98190.36755138682</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1908409</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1908409.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>13.93</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>13.97</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>13.97</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>3569984.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>4248241.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>4248241.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3563303.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>3104951.66</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>3104951.66</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>289427.6874827892</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>3569984</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>3569984.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>13.96</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>6544906.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>4640304.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>4640304.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3628178.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>3073685.66</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>3073685.66</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>374261.262831836</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>6544906</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>6544906.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2448293.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>3721085.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>3721085.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>3190101.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2994918.16</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2994918.16</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>163343.9682293362</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2448293</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2448293.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>14.0</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>7026681.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>3664563.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>3664563.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>3355479.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2989685.52</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2989685.52</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>295122.6556461463</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>7026681</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>7026681.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>13.98</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1651342.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2657816.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2657816.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2952051.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2890366.76</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2890366.76</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-17703.74288863037</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1651342</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1651342.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>14.02</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>13.94</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>13.99</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>13.99</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5530299.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2878365.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2878365</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>3145289.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>2900636.62</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>2900636.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>111962.8571648546</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5530299</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5530299.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>36.63</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>36.84</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>37.66</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>37.66</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>948983287.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>481073165.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>481073165</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>668625815.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>545623182.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>545623182.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>26510587.29221785</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>948983287</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>948983287.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>35.95</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>36.76</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>37.65</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>37.65</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>396972349.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>513225661.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>513225661</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>631793141.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>554943688.88</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>554943688.88</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-7936822.118145883</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>396972349</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>396972349.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>35.89</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>36.76</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>37.69</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>37.69</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>300374611.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>536197886.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>536197886.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>618160682.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>641008727.94</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>641008727.9400001</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>2280080.014125466</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>300374611</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>300374611.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>36.25</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>36.84</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>37.75</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>36.84</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>37.75</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>418443319.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>640847468.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>640847468.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>617293114.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>647605587.46</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>647605587.46</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>27143980.70258009</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>418443319</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>418443319.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>36.85</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>37.81</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>37.81</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>340592259.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>813398701.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>813398701.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>598360583.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>657316092.18</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>657316092.1799999</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>49044192.23242319</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>340592259</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>340592259.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>37.25</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>37.06</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>37.85</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1109745767.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>856178466.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>856178466</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>584464696.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>670145522.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>670145522.3</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>86919815.40961254</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1109745767</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1109745767.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>37.76000000000001</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>37.22</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>37.91</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>511833478.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>750360622.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>750360622</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>491817475.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>670427143.82</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>670427143.8200001</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>55514264.96953964</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>511833478</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>511833478.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>37.75</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>37.29</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>37.93</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>823622518.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>700123477.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>700123477.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>481822221.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>682294890.78</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>682294890.78</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>72728571.55623758</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>823622518</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>823622518.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>37.59</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>37.33</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>37.93</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1281199485.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>593738760.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>593738760.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>426910925.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>672562700.82</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>672562700.8200001</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>61317020.55308324</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1281199485</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1281199485.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>37.17999999999999</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>37.33</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>37.92</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>37.92</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>554491082.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>383322465.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>383322465.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>330296682.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>661412051.02</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>661412051.02</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-6201192.364032865</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>554491082</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>554491082.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>36.95</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>37.37</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>37.94</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>580656547.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>312750926.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>312750926.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>308101964.8</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>665608466.64</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>665608466.64</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-24572696.4826262</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>580656547</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>580656547.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>22.84</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>23.7</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>23.7</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>6332270.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>4624239.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>4624239</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>6243180.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>8391838.62</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>8391838.619999999</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-578987.4455218827</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>6332270</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>6332270.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>22.69</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>23.72</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>23.72</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>3548658.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>4594941.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>4594941.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>6375984.2</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>8465061.2</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>8465061.199999999</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-695819.9382180348</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>3548658</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>3548658.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>22.58</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>23.23</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>23.76</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>23.76</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>7042514.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>6555103.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>6555103.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>7415488.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>8510275.52</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>8510275.52</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-539628.6442761794</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>7042514</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>7042514.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>22.58</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>23.81</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>23.81</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>2873085.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>6496499.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>6496499.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>8130069.0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>8463017.46</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>8463017.460000001</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-671567.4870636659</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>2873085</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>2873085.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>22.74</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>23.87</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>23.87</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>3324668.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>7392636.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>7392636</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>8448981.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>8484849.54</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>8484849.539999999</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-389342.4593649451</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>3324668</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>3324668.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>22.84</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>23.41</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>23.93</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>23.93</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>6185784.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>7862122.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>7862122.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>8601948.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>8524383.08</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>8524383.08</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-20642.65338945109</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>6185784</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>6185784.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>22.96</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>23.99</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>13349467.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>8157026.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>8157026.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>8436643.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>8640495.58</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>8640495.58</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>200260.4499108754</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>13349467</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>13349467.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>23.02</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>23.52</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>24.04</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>24.04</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>6749493.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>8275873.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>8275873.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>7565662.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>8473081.88</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>8473081.880000001</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-258853.3114426173</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>6749493</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>6749493.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>23.03</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>24.08</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>24.08</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>7353768.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>9763638.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>9763638.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>7402091.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>8441252.42</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>8441252.42</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-198345.2808246566</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>7353768</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>7353768.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>23.12</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>23.56</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>24.11</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>24.11</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>5672102.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>9505326.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>9505326.199999999</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>7070988.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>8425331.36</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>8425331.359999999</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-169565.2270552609</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>5672102</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>5672102.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>23.25</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>24.15</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>24.15</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>7660303.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>9341773.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>9341773.199999999</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>7051896.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>8484251.38</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>8484251.380000001</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>57783.53643870726</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>7660303</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>7660303.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>14.49</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>14.55</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>15.23</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>122168820.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>55877303.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>55877303.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>50099375.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>59366944.36</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>59366944.36</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>4085064.155979253</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>122168820</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>122168820.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>14.26</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>14.54</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>15.24</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>15.24</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>29289673.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>37332423.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>37332423.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>41294690.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>58747134.16</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>58747134.16</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-2418366.581848741</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>29289673</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>29289673.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>14.18</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>14.58</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>15.26</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>15.26</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>56373070.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>38065328.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>38065328.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>42507010.0</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>59897788.2</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>59897788.2</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1671274.507965557</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>56373070</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>56373070.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>14.22</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>14.64</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>15.29</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>15.29</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>42160227.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>33319286.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>33319286.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>39386768.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>59943683.6</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>59943683.6</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-3446104.277133673</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>42160227</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>42160227.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>14.39</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>15.32</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>15.32</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>29394728.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>36082103.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>36082103</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>36726915.8</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>60196307.34</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>60196307.34</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-4335695.616047643</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>29394728</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>29394728.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>14.52</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>14.78</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>15.35</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>29444419.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>44321448.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>44321448.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>36990831.2</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>61119707.72</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>61119707.72</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-4083962.078208745</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>29444419</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>29444419.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>14.6</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>14.86</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>15.39</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>32954199.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>45256957.4</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>45256957.4</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>36579452.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>62794805.98</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>62794805.98</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-3583810.985645726</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>32954199</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>32954199.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>14.6</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>15.42</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>32642859.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>46948691.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>46948691.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>38146731.5</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>62991916.04</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>62991916.04</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-3117364.032496922</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>32642859</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>32642859.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>14.57</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>14.99</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>15.45</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>55974310.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>45454251.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>45454251.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>39491259.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>64102186.58</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>64102186.58</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-2306318.95540946</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>55974310</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>55974310.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>14.53</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>15.03</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>15.48</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>15.48</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>70591454.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>37371728.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>37371728.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>40590135.2</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>65990743.12</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>65990743.12</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-3565112.918305591</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>70591454</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>70591454.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>14.52</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>15.07</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>15.5</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>34121965.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>29660214.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>29660214.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>40310844.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>65986839.24</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>65986839.24</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-6802187.118217729</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>34121965</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>34121965.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>27.32</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>27.32</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>922889.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>405378.6</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>405378.6</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>562072.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>418350.92</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>418350.92</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>21506.4770962398</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>922889</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>922889.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>28.1</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>27.76</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>27.26</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>27.26</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>434795.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>325239.0</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>325239</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>528479.1</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>428076.44</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>428076.44</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-17026.39684747037</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>434795</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>434795.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>27.96</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>27.22</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>27.22</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>280586.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>352472.0</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>352472</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>533293.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>422026.78</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>422026.78</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-19169.48830821813</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>280586</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>280586.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>27.88</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>27.66</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>27.19</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>27.66</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>27.19</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>238141.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>642925.8</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>642925.8</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>519276.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>425600.48</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>425600.48</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-5024.030098278541</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>238141</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>238141.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>27.86</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>27.63</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>27.16</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>27.16</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>150482.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>701389.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>701389.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>531653.6</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>436635.56</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>436635.56</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>19910.87556228798</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>150482</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>150482.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>27.78</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>27.58</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>27.12</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>27.12</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>522191.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>718765.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>718765.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>569184.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>457466.5</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>457466.5</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>64213.10237872985</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>522191</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>522191.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>27.76</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>27.54</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>27.07</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>27.07</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>570960.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>731719.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>731719.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>564833.7</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>448558.68</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>448558.68</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>85382.70846012083</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>570960</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>570960.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>27.03</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>27.03</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>1732855.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>714114.6</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>714114.6</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>569415.9</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>441124.92</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>441124.92</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>107350.3704171036</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>1732855</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>1732855.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>27.47</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>26.98</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>26.98</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>530460.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>395627.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>395627.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>451171.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>411292.72</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>411292.72</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>10410.05284075369</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>530460</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>530460.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>27.76</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>27.44</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>26.93</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>237361.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>361917.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>361917.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>409681.8</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>406819.52</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>406819.52</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>380.1329873698996</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>237361</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>237361.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>27.73</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>27.39</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>26.88</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>27.39</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>26.88</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>586960.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>419603.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>419603.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>470592.1</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>416157.3</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>416157.3</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>17441.5641615584</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>586960</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>586960.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>28.2</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>1203482068.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1387618376.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1387618376.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>4264040487.3</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>3111629550.18</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>3111629550.18</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-488176249.5318046</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1203482068</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1203482068.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>30.16</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>28.07</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>30.16</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>28.07</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>942023312.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1584381817.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1584381817</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>4484329546.0</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>3097694126.7</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>3097694126.7</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-425650424.2230182</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>942023312</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>942023312.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>29.25</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>30.24</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>27.94</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>1007778782.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>2139497377.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>2139497377.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>4665494634.0</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>3096337448.26</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>3096337448.26</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-293112577.631073</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1007778782</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1007778782.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>29.73</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>30.32</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>30.32</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>27.81</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1607084998.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>3258049059.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>3258049059.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>4688553902.3</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>3083594155.06</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>3083594155.06</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-100349719.3700418</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1607084998</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1607084998.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>30.62</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>27.69</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>27.69</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>2177722724.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>5262265961.4</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>5262265961.4</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>4687463430.7</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>3075231109.06</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>3075231109.06</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>114398330.6946478</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>2177722724</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>2177722724.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>31.58</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>27.56</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>27.56</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>2187299269.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>7140462597.8</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>7140462597.8</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>4678699401.4</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>3064464439.28</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>3064464439.28</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>355955848.3336811</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>2187299269</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>2187299269.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>32.04</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>30.44</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>27.46</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>27.46</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>3717601115.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>7384277275.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>7384277275</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>4600886187.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>3041422265.56</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>3041422265.56</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>687299249.1275253</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>3717601115</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>3717601115.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>32.03</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>27.29</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>30.45</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>27.29</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>6600537191.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>7191491890.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>7191491890.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>4454153458.5</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2973288757.28</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2973288757.28</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>972139650.7213211</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>6600537191</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>6600537191.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>30.34</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>27.1</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>27.1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>11628169508.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>6119058745.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>6119058745.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>3965899981.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2847760321.4</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2847760321.4</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>1035449228.758123</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>11628169508</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>11628169508.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>30.19</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>26.9</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>11568705906.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>4112660900.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>4112660900</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>2972243250.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2623033685.92</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2623033685.92</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>550236262.3907671</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>11568705906</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>11568705906.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>30.27</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>26.66</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>26.66</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>3406372655.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>2216936205.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>2216936205</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>2119863690.1</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2406749639.6</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2406749639.6</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-156205313.0051274</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>3406372655</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>3406372655.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
